--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soPriceChange.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soPriceChange.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>单据编号</t>
   </si>
@@ -47,22 +47,16 @@
     <t>区间从-到</t>
   </si>
   <si>
-    <t>调整前含税单价</t>
-  </si>
-  <si>
     <t>调整后含税单价</t>
   </si>
   <si>
-    <t>调价前税率(%)</t>
-  </si>
-  <si>
-    <t>调整后税率(%)</t>
-  </si>
-  <si>
     <t>销售组织</t>
   </si>
   <si>
-    <t>生效时间</t>
+    <t>新生效时间</t>
+  </si>
+  <si>
+    <t>新失效时间</t>
   </si>
   <si>
     <t>升降比例</t>
@@ -101,16 +95,7 @@
     <t>{.qtySection}</t>
   </si>
   <si>
-    <t>{.oldTaxPrice}</t>
-  </si>
-  <si>
     <t>{.taxPrice}</t>
-  </si>
-  <si>
-    <t>{.oldTaxRate}</t>
-  </si>
-  <si>
-    <t>{.taxRate}</t>
   </si>
   <si>
     <t>{.soOrgName}</t>
@@ -1327,21 +1312,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
     <col min="4" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="11.375" customWidth="1"/>
-    <col min="8" max="8" width="10.875" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:18">
+    <row r="1" ht="30" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1390,67 +1372,55 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soPriceChange.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soPriceChange.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>单据编号</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>{.effectiveDate}</t>
+  </si>
+  <si>
+    <t>{.expireDate}</t>
   </si>
   <si>
     <t>{.offsetRate}</t>
@@ -1402,25 +1405,25 @@
         <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
